--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45043</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>46052</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45463</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45376</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44490</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45035</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>46026</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>46087</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45194</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44868</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44477</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45618</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44886</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>45621</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45254</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45915</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44977</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44977</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>45622</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44999</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45701</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45436</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>46037</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>46127</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45239</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45463</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>46212</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>46260</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>46279</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45260</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44617</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44778</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44634</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44558</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44658</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44477</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44558</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44692</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44783</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44526</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44617</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44620</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44837</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44839</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44558</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>44552</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44459</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44558</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44491</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44841</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44800</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44529</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44480</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44543</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44620</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44620</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45469</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45369</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44946</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45392</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45659</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45565</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45565</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45751</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45646</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45582</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>45142</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44897</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45390</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45278</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45701</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45573</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45328</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45462</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45035</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45496</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45205</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45618</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44854</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>45463</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>44861</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44859</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45688</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44867</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45638</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45688</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45603</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45385</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>44966</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>45463</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45469</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45661</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45561</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45635</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>45463</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45040</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44832</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45484</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44503</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45677</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45496</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45505</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45393</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45110</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45659</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45702</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44810</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45632</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44994</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45224</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45279</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45086</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45399</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45679</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45469</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45356</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45160</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44746</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45341</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45224</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45663</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45420</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45208</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>44477</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>44477</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46026</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45884</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>44741</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44610</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45225</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45884</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44735</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45826</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45889</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45670</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>45643</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45896</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45890</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45575</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45890</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45886</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45296</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45642</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45886</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45035</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45909</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>45580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44981</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45897</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45909</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45342</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44657</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>46034</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44897</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>44897</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44741</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45831</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45841</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45771</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45910</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45664</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45664</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45664</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45880</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46140</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45589</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45917</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>44977</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44977</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45496</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45187</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44617</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>46100</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44664</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45560</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45560</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45925</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45925</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45371</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45932</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45932</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>45936</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>45936</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>45000</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>45629</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45938</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45939</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>44565</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45646</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45701</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45943</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45943</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45945</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45945</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46148</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45712</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45946</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45946</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>46148</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45224</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44876</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45947</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>46149</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>46149</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45553</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45949</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>45161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45953</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>44973</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45952</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>44974</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45687</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45953</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45381</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46153</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45956</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45691</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45958</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44909</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45215</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>44459</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45965</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45247</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>46155</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45965</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45965</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45533</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>44859</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45712</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45968</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45098</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>45098</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45706</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>46155</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45385</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>45385</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45251</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45975</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45708</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45708</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45708</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45729</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45303</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45161</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45476</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45988</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45708</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>45989</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45992</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45992</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45992</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45992</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45992</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45740</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45740</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>45992</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>45993</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>45990</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>44883</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>46009</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46159</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>46162</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46162</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46163</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45685</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>45756</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>44895</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45035</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45992</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45992</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45992</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45670</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>45758</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45596</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45691</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45995</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45999</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45996</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45996</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>46104</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45001</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>46000</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44867</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>46001</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45679</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45756</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>45183</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>45433</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>46149</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44890</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46007</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>46027</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45378</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>46097</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>46005</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45412</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45558</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>46168</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>46010</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46010</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45635</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45635</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44546</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46010</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>46012</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46010</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45443</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>46010</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>46168</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45635</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45484</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45644</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46168</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>44490</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>46168</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>46018</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>46020</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45470</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>46020</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>46021</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45691</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45691</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>44852</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>46030</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46034</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>46035</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>46035</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45350</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45379</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>46174</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>45112</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>46037</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>46037</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>46041</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46045</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>46010</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45344</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>45264</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45075</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45012</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>46059</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>44897</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45562</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46065</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>46065</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46183</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46183</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45077</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46181</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45688</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46183</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46182</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46182</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>46182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>46076</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45596</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46076</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46076</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>46076</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45665</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46079</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46080</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45379</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45412</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46090</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45232</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>44496</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45054</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45379</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45091</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45212</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>45212</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>46100</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>46100</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>46100</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>46100</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>46099</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45562</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46100</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>46104</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>46104</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>46104</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>46104</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>46104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45040</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>46105</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>45664</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45077</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45225</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44579</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45204</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>46197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45264</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45323</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>45106</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46202</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45342</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45016</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44546</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>46199</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>46200</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45807</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>45463</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46202</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46133</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44960</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>44960</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45826</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45232</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>46000</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44722</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45664</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44872</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45749</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>46247</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44985</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>46206</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44917</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>44580</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45663</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45309</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45098</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45204</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45255</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45530</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45411</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45411</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45104</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45323</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>44897</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45618</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45327</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46259</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>46213</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46259</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45663</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45720</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44859</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45527</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44610</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45392</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>44897</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45960</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>44966</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>46136</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45379</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46138</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45723</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46262</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45013</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>46265</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>46161</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45676</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45501</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46265</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>46262</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45653</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45328</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45441</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45639</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>46269</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46269</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>46268</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>44995</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>46269</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45692</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>46230</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>44463</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>46273</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>46231</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>46231</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>46275</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>46231</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>46168</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>44914</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45939,7 +45939,7 @@
         <v>45683</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>46279</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>46279</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>46279</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>46279</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>46279</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46237</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>46238</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>46237</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>46238</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>46238</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>46281</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>46281</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>45219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45792</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>46238</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>46238</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>46238</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>46238</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>46238</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45792</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>46282</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>46282</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45499</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45140</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45699</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>44859</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46240</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45659</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45639</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>46283</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45700</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45688</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>45660</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45978</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>46241</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>46241</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>46282</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45330</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>45230</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>45813</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45824</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45826</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45827</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45827</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45827</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45827</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45831</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45694</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45835</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>45835</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>45835</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45835</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45835</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45841</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45841</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45847</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45847</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45685</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45859</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45881</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45880</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44944</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>44739</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44956</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45476</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>44945</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45028</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>46189</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46052</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45043</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45433</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45463</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45035</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>46099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45664</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45824</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45376</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45412</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46026</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45194</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45239</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44868</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44477</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44886</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45436</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>46037</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45915</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44951</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45618</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46127</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45621</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>45834</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44999</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44977</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45463</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>46190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45254</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45572</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>46212</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45701</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>45239</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44617</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44778</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44634</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44558</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44658</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44477</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44558</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44692</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44783</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44526</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44617</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44620</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44837</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44839</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44558</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>44552</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44558</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44491</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44841</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44800</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44529</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44480</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44620</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44620</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45327</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45212</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45212</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>45412</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45392</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45204</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45385</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45379</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45224</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45098</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>44477</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44477</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45463</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45505</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45659</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>46012</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45463</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>46018</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46020</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46020</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45699</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44859</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45639</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45499</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45140</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45035</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45884</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45660</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45884</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45603</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45341</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45330</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46034</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>46035</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45886</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46035</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45890</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>46041</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44859</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44859</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45688</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45897</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45663</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>46045</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>46010</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44985</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44854</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44861</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45558</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44897</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44897</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>45915</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44960</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45915</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46065</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45390</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>46065</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45751</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45925</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46076</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45925</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46076</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46076</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45009</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45639</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46079</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45688</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46080</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45932</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45932</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45230</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45936</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45530</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45936</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>46091</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45224</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45208</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45939</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45943</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46099</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>46100</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>46100</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>46100</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45945</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45946</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45946</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>46100</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45945</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45945</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45945</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45947</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>46104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>46104</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>46105</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45947</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>46104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>46104</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>46104</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45575</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>44867</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45954</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45953</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45350</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45956</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45958</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45573</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45807</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45965</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45965</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>45965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45968</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45618</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45012</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45813</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45974</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45629</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45708</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45708</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45708</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45679</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45077</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45981</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45646</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45661</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45646</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45712</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45323</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45692</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45988</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45992</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45701</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45989</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45659</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45161</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45992</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45708</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45740</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45990</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45992</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45664</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45993</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>46140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45996</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44610</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45664</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45996</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44810</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45880</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45996</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45999</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>46100</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>46000</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>46001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45691</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44657</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>46000</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>46006</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45496</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>44832</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45476</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>46007</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45691</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45691</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45035</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45826</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45896</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46010</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>46010</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46026</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45670</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46010</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45635</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45635</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45635</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>46010</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45443</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>46005</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45589</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46010</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44966</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45369</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>44617</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45909</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>46140</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45040</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45013</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45831</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45824</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45749</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45111</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46104</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45826</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45909</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45187</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46002</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45826</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46034</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44883</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45664</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45664</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45496</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45496</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45596</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45688</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45412</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44897</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45841</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45827</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45702</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45827</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>45827</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45827</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45054</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45077</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>46148</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>46148</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45701</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44897</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45463</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>46149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>46149</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45831</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46153</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45687</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45086</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45694</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46155</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45714</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45835</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>46155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45835</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45835</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45835</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>46009</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45835</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45106</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>46159</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45496</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45756</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45758</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44664</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46162</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45381</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45841</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>44872</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46162</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44490</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45379</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>46149</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>46163</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>45847</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45378</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45433</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45847</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>46104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45685</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45679</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>45392</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>46168</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>46168</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>46027</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>46097</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46168</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45562</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45110</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45859</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45075</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45303</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45463</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45040</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45112</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>44546</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>44546</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>46181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45706</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45161</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46181</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46183</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46183</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>46182</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>46182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44610</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>44503</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45484</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44994</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>45399</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>45533</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45379</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45016</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44995</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45643</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45323</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45664</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46200</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>46199</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45881</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45644</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>46202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>46202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45880</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45653</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>46202</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>46206</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45729</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45204</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45629</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45385</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45224</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45225</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45225</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>45665</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45098</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46213</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45670</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>45251</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46259</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46259</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45960</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46262</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45527</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>46262</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44852</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>44741</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45205</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>44735</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45278</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45723</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46136</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>46265</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>46138</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>46161</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45255</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46265</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45501</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>44746</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>46268</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44722</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>44741</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46269</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45160</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46269</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45469</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>46269</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44859</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>46231</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46231</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46230</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>46231</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>46273</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45264</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46275</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45342</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46279</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>46279</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>46237</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46279</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46237</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45247</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45328</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45484</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>46282</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>46282</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>46238</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>46238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46238</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46238</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46238</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>46238</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>46238</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>46238</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45582</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46281</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>46281</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45646</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>46240</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>46168</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>44960</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>46286</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46283</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>44890</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>44917</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>44565</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45910</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>46241</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46241</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45890</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45000</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>46287</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45562</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>46287</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45565</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45565</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45560</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45560</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45978</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>44909</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>44987</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46076</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>46247</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45344</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>46289</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45183</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45756</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45561</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45001</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46174</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45411</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45411</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>44496</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44867</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45035</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>44579</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45642</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45470</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45232</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45618</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45670</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44981</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>44977</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>44977</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45342</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>44973</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>44974</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45469</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45356</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45215</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45677</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45558</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45371</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45328</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>45462</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>44876</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45635</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45309</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45663</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45264</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45553</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45720</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>45712</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45379</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45659</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45580</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45279</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>44580</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45663</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45676</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45296</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>44946</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>44897</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>44897</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45638</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45691</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45441</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45664</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45688</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45683</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>44914</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45792</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45219</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45792</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44739</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>44944</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44956</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45476</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>44945</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45028</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>46189</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46052</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45043</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45995</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45433</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45463</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45035</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>46099</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>45664</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45824</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44490</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45376</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45412</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46026</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45194</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45239</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44868</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44477</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44886</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45436</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>46037</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>45915</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>44951</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45618</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46127</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45621</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45835</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>45834</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44999</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44977</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45463</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>46190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45622</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45254</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45572</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>46212</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45701</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>45239</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44617</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44778</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44634</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44558</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44658</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44477</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44558</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44692</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44783</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>44526</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44617</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44620</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44837</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44839</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44558</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44789</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>44552</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44558</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44491</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44841</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44800</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44529</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44480</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44543</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44620</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44620</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45327</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45212</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45212</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>45412</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45392</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45204</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45393</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45385</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45385</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45379</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45224</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45098</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>44477</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44477</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45463</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45505</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45659</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>46012</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>45463</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>46018</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46020</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46020</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45699</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44859</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45639</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45499</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45140</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45035</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45884</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45660</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45884</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45603</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45341</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45330</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46034</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>46035</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45886</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46035</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45890</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>46041</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44859</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44859</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45688</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45897</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45663</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>46045</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>46010</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44985</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44854</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44861</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45558</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44897</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44897</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>45915</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>44960</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16922,7 +16922,7 @@
         <v>45915</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46065</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45390</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>46065</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45751</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45925</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46076</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45925</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46076</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46076</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45009</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45639</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46079</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45688</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46080</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45932</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45932</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45230</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45936</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45530</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45936</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>46091</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45224</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45208</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45939</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45943</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46099</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>46100</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>46100</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>46100</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45945</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45946</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45946</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>46100</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45945</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45945</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45945</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45947</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>46104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>46104</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>46105</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45947</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>46104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>46104</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>46104</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45575</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>44867</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45954</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45953</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45350</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45956</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45958</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45573</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45807</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45965</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45965</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>45965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45968</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45618</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45012</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45813</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45974</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>45978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45629</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45708</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45708</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45708</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45679</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45077</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45981</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45646</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45661</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45646</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45712</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45323</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45692</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45988</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45992</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45701</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45989</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45992</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45659</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45161</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45992</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45992</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45708</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45740</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45990</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45992</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45664</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45993</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>46140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45996</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44610</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45664</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45996</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44810</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45880</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45996</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45999</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>46100</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>46000</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>46001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45691</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44657</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>46000</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>46006</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45496</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>44832</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>46008</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45476</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>46007</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45691</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45691</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45035</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45826</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45896</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46010</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>46010</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46026</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45670</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46010</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45635</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45635</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45635</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>46010</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45443</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>46005</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45589</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46010</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44966</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45369</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>44617</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45909</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>46140</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45040</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45013</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45831</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45824</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45749</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45111</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46104</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45826</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44895</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45909</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45187</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46002</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45826</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46034</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44883</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45664</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45664</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45496</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45496</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45596</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45688</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45412</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44897</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45841</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45827</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45702</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45827</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>45827</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45827</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45054</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45077</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>46148</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>46148</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45701</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44897</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45463</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>46149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>46149</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45831</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>46153</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45687</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45086</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45694</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46155</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45714</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45835</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>46155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45835</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45835</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45835</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>46009</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45835</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45106</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>46159</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45496</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>45756</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45758</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44664</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46162</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45381</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45841</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>44872</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46162</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44490</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45379</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>46149</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>46163</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34222,7 +34222,7 @@
         <v>45847</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45378</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45433</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45847</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>46104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45685</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45679</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>45392</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>46168</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>46168</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>46027</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>46097</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46168</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45562</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45110</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45859</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45075</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45303</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45463</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45040</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45112</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>44546</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>44546</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>46181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45706</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45161</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46181</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46183</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46183</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>46182</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>46182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44610</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>44503</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45484</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44994</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>45399</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>45533</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45379</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45016</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44995</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45643</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45323</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>45664</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46200</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>46199</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45881</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45644</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>46202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>46202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45880</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45653</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>46202</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>46206</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45729</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45204</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45629</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>45385</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45224</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45225</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>45225</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>45665</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45098</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46213</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45670</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>45251</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46259</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46259</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45960</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>46262</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45527</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>46262</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44852</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>44741</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45205</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>44735</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45278</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45723</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46136</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>46265</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>46138</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>46161</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45255</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46265</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45501</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>44746</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>46268</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>44722</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>44741</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46269</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45160</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46269</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45469</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>46269</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44859</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>46231</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46231</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46230</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>46231</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>46273</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45264</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46275</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45342</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46279</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>46279</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>46237</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46279</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46237</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45247</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45328</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>45484</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>46282</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>46282</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>46238</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>46238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>46238</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46238</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46238</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>46238</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>46238</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>46238</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45582</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46281</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>46281</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45646</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>46240</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>46168</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>44960</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>46286</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46283</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>44890</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>44917</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>44565</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45910</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>46241</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46241</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45890</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45000</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>46287</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45562</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>46287</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45565</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45565</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45560</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45560</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45978</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>44909</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>44987</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46076</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>46247</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45344</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>46289</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45183</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45756</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45561</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45001</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46174</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45411</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45411</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>44496</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44867</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45035</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>44579</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45642</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45470</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45232</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45618</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45670</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44981</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>44977</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>44977</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45342</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>44973</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>44974</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45469</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45356</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45215</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45677</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45558</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45371</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45328</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>45462</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>44876</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45635</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45309</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45663</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45264</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45553</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45720</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
         <v>45712</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45379</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45659</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49143,7 +49143,7 @@
         <v>45580</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45279</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>44580</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45663</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45676</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45296</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>44946</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>44897</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>44897</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45638</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45691</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49946,7 +49946,7 @@
         <v>45441</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45664</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45688</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45683</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>44914</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45792</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45219</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45792</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>44739</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>44944</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44956</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45476</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>44945</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45028</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>46189</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46052</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45433</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45995</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45463</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45376</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45664</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45035</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46026</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45194</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46279</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44473</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44868</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44477</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46037</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45915</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45618</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45254</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>46127</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45834</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44977</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45826</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45572</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45701</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>46190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45436</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46260</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44951</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>46279</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>46212</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45239</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45463</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>46296</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46296</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44868</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44481</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44617</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44852</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44854</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44778</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44634</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44635</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44558</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44852</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44746</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44868</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44634</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44741</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44558</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44658</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44477</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44676</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44692</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44746</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44783</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44526</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44617</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44620</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44837</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44550</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44789</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44491</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44841</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44800</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44529</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44480</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44543</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44620</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44620</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44852</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44558</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44558</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45469</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45369</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>44897</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45392</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45659</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45035</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45565</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45565</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45278</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44987</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45582</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45751</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45646</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45646</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45618</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45142</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>46001</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45390</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45701</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45573</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45462</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45205</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>46006</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44859</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>46007</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>46005</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45884</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46008</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45887</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>46010</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45635</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45635</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44854</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>46010</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46012</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46010</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45443</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46010</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45635</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45463</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>46018</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45558</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>46020</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>46020</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>46021</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44861</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45890</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44859</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>46030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>46034</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45219</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>46035</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>46035</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45688</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>46037</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45792</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46041</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45499</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45699</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44859</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45659</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46010</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45915</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45688</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45917</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45688</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45660</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45603</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45330</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45230</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45925</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45925</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45385</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>46059</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45463</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45469</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45635</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45932</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45561</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45040</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46065</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46065</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45932</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45936</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45661</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45463</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44832</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45938</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45484</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>44503</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45943</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45943</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45945</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45945</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45393</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45945</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45945</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45496</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45496</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45946</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45946</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>46076</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45677</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45947</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45505</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>46076</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>46076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45950</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45110</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45949</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>46079</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46080</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45659</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45813</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45953</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45702</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45954</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45956</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45958</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>44937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>46091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45965</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>44810</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45965</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45965</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45224</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44994</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45968</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45632</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>46100</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>46100</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46099</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45971</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>46100</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45111</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45160</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45208</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>46104</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45086</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46104</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46104</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>46104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46104</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46105</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45975</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45708</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45708</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45708</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45978</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45399</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45978</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45679</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45981</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45356</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45663</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45469</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>44746</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45224</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45988</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45708</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45989</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45824</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45992</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45992</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45992</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45992</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45826</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45992</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45740</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45807</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45993</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45990</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45992</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45827</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44477</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44477</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45995</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44741</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45996</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45999</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45996</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45827</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45996</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45827</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45831</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45225</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>46000</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>46133</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45113</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>44735</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45694</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45835</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45835</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45575</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45835</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45009</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45835</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45835</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45296</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46000</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45642</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45841</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45841</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45664</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45035</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45580</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45749</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44981</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45342</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>46026</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>46002</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45847</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45847</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>44897</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44897</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>44610</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44741</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45771</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45664</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45664</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45685</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45826</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>46104</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44977</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44977</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45896</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44617</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44664</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45560</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45560</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45664</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45909</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45859</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45909</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>44657</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45371</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>46034</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>45841</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45000</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45664</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45629</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45880</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46140</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45981</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44565</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45646</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45496</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45187</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>46100</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45712</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45224</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46140</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44876</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45553</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45161</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>44973</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>44974</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45701</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45381</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46148</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>46149</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>46149</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45687</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44909</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45215</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>46155</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45247</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45533</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44859</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45712</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>46155</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45714</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45098</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45098</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45706</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>46009</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46159</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45385</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45385</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>46162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>46162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>46163</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45685</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45756</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45758</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45729</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45303</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46104</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45629</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45679</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45433</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46149</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46027</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45378</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46097</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>46168</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>46168</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45161</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45881</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46168</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45880</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45476</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>44883</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45886</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>46183</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>46183</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>46181</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44895</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45035</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>46181</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45670</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>46183</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46182</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>46182</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46182</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45596</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45691</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45001</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44867</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45379</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>44890</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45412</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45558</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44546</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45484</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45644</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46197</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44490</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46202</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46202</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45470</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>46199</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>46200</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45691</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45691</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>46202</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44852</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46206</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45350</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45379</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45112</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>46259</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46213</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46259</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45344</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45527</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45960</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45264</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45075</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>46136</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>46138</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45012</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45723</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>46262</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>46265</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>46161</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45501</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>46265</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>46262</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>44897</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45562</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45077</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>46269</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46269</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>46268</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45688</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46269</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45255</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45596</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46230</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>46273</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45665</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>46231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>46275</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>46231</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>46279</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>46279</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>46279</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>46279</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>46279</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>46237</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45412</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>46238</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46237</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>46238</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46238</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45232</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>46281</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>46238</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46238</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>46238</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>46238</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46238</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46282</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46282</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46240</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44496</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45054</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45091</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45212</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45212</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45562</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46282</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45040</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45890</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45664</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45910</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45077</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46241</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>46241</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45225</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46286</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>44579</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45204</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>46076</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>46168</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>46287</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46287</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45264</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45323</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45106</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45342</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45016</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>44546</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45463</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>46291</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>46174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>45756</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>46247</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>46293</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>46293</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>44960</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>46294</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>44960</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>46295</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45232</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>44722</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>46294</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>44872</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44985</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>46296</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>46296</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>44917</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45978</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>44580</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45663</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>45309</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45098</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45204</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45255</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45530</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45411</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45411</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45323</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44897</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45618</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45327</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45663</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45720</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44859</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>44610</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45392</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>44897</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>44966</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45379</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45013</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45676</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45653</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45328</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45441</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>45639</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>44995</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45692</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>44914</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45683</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>44944</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>44739</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>44956</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45476</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>44945</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45028</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>46189</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46052</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45433</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45995</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45463</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45376</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45664</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45035</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46026</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45194</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45642</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46279</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>44473</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>46008</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>44868</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44477</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45708</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46037</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45915</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45618</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45621</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45254</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>46127</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45834</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44977</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45826</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45622</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45572</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45701</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>46190</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45436</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>46260</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44951</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>46279</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>46212</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>45239</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45463</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>46296</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46296</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44868</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44481</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>44617</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44852</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44854</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44778</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44634</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44635</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44558</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44852</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44746</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44868</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44634</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44741</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44558</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44658</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44477</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44676</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44692</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44746</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44783</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44526</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44617</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44620</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44837</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44550</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44789</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44491</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44841</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44800</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44529</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44480</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44543</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44620</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44620</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44852</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44558</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44558</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45469</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45369</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>44897</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45392</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45659</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45035</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45565</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45565</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45278</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44987</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45582</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45751</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45646</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45646</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45618</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45142</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>46001</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45390</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>45701</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45573</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45462</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45205</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>46006</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44859</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>46007</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>46005</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45884</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46008</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45887</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>46010</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45635</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45635</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44854</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>46010</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46012</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46010</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45443</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46010</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45635</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45463</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>46018</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45558</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>46020</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>46020</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>46021</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>44861</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45890</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44859</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>46030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>46034</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45219</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>46035</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>46035</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45688</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>46037</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45792</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>46041</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45499</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45699</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>44859</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45659</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45639</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45915</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46010</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45915</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45688</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45917</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45688</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45660</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45603</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45330</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45230</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45925</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45925</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45385</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>46059</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45463</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45469</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45635</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45932</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45561</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45040</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46065</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46065</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45932</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45936</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45661</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>45463</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44832</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45938</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45484</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>44503</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45943</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45943</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45945</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45945</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45393</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45945</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45945</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45496</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45496</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45946</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45946</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>46076</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45677</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45947</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45505</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>46076</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>46076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45950</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45110</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45949</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>46079</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46080</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45659</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45813</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45953</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45702</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45954</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45956</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45958</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>44937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>46091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45965</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>44810</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45965</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45965</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45224</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45279</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44994</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45968</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45632</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>46100</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>46100</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46099</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45971</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>46100</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45111</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45160</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45208</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>46104</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45086</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46104</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46104</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>46104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46104</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46105</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45975</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45708</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45708</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45708</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45978</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45399</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45978</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45679</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45981</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45356</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45663</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45469</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>44746</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45224</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45988</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45708</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45989</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45824</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45992</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45992</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45992</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45992</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45826</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45992</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45740</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45992</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45807</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45993</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45990</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45992</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45827</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44477</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44477</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45995</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>44741</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45996</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45999</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45996</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45827</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45996</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45827</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45831</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45225</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>46000</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>46133</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45113</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>44735</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45694</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45835</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45835</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29213,7 +29213,7 @@
         <v>45575</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45835</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>45009</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45835</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45826</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45835</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45296</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46000</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45642</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45841</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45841</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45664</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45035</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45580</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45749</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44981</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45342</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>46026</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>46002</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>45847</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45847</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>44897</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44897</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>44610</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44741</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45771</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45664</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45664</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45685</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45826</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>46104</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>44977</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44977</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45896</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44617</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44664</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45560</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45560</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45664</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45909</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45859</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45909</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>44657</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45371</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>46034</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>45841</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45000</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45664</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45629</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45880</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>46140</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45981</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44565</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45646</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45496</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45187</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>46100</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45712</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45224</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46140</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44876</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45553</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45161</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>44973</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>44974</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45701</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45381</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46148</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>46149</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>46149</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45687</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44909</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45215</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>46155</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>45247</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45533</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44859</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45712</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>46155</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45714</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45098</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45098</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45706</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>46009</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46159</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45385</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45385</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>46162</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>46162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>46163</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45685</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45756</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45758</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45729</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45303</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46104</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45629</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45679</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45433</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46149</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46027</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45378</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46097</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>46168</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>46168</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45161</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45881</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46168</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45880</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45476</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45670</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>44883</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>45886</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>46183</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>46183</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>46181</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44895</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45035</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>46181</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45670</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>46183</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>46182</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>46182</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>46182</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45596</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45691</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45001</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44867</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45379</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>44890</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45412</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45558</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44546</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45484</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45644</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46197</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44490</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46202</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46202</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45470</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>46199</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>46200</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45691</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45691</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>46202</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44852</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46206</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45350</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45379</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45112</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>46259</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46213</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46259</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45344</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45527</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45960</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45264</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45075</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>46136</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>46138</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45012</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45723</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>46262</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>46265</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>46161</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45501</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>46265</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>46262</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>44897</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45562</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45077</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>46269</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46269</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>46268</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45688</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>46269</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45255</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45596</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46230</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>46273</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45665</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46231</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>46231</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>46275</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>46231</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>46279</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>46279</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>46279</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>46279</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>46279</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>46237</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45412</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>46238</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46237</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>46238</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46238</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45232</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>46281</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>46238</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46238</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>46238</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>46238</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46238</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46282</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>46282</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46240</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>44496</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45054</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45091</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45212</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45212</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45562</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46282</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45040</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45890</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45664</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45910</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45077</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46241</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>46241</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45225</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46286</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>44579</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45204</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>46076</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>46168</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>46287</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46287</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45264</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45323</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45106</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45342</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45016</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>46289</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>44546</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45463</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>46291</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>46174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>45756</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>46247</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>46293</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>46293</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>44960</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>46294</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>44960</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>46295</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45232</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>44722</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>46294</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>44872</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44985</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>46296</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>46296</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>44917</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45978</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>44580</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45663</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>45309</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45098</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45204</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45255</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45530</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45411</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45411</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45104</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45323</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44897</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45618</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45327</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45663</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45720</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>44859</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>44610</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45392</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>44897</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>44966</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45379</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45013</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45676</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45653</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45328</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45441</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>45639</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>44995</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45692</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>44914</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45683</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>44944</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>44739</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>44956</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45476</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>44945</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45028</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>46189</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45412</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>44490</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45035</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45712</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45376</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45194</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45642</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>46026</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>46087</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46008</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>44868</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44886</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44999</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45239</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45436</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44977</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45463</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>45915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45622</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44951</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45618</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45254</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45251</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45572</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45826</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>46037</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45701</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44977</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45835</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>46190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>46279</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46212</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>46296</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>46296</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44481</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44617</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44778</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44550</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44634</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44558</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44658</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44550</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44789</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44480</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44617</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44676</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44558</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44552</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44543</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44841</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>44746</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>44620</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44837</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44800</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44839</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44526</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44529</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44558</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44620</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44620</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45412</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45392</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45204</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45677</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44897</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45463</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45558</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45462</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45385</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45385</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45635</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45309</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45106</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45393</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45663</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45327</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44664</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44859</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45379</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45264</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45381</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45224</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45098</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45553</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45720</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44490</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45379</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45712</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45212</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45379</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45659</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45392</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45463</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45562</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45505</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45279</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45463</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45110</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44580</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45886</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45663</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45887</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45676</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45296</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44946</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45075</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44897</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45603</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45889</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45890</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45799</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45341</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45691</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45303</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45463</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45441</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44859</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>44859</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45040</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44546</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44546</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45688</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45632</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45663</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45706</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45161</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44985</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>44854</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44861</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44503</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45484</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45558</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44897</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45771</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45399</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45533</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44937</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45390</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45683</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44914</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45016</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45751</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45792</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45219</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45925</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45643</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45323</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45792</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45009</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45232</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45639</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45659</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45664</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45699</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45688</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44859</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45639</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45932</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45499</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45140</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45700</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45660</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45644</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45530</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45330</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45224</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45208</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45936</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45653</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45688</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45142</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45729</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45091</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45230</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45204</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45385</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45224</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45938</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45939</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45943</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45575</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>44867</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45943</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45225</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45945</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45225</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45946</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45946</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45813</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45350</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45950</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45665</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45947</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45949</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45573</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>45098</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45670</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45824</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45826</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45827</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45827</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45827</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45827</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45618</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45251</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45954</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45953</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45012</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45956</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45958</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45831</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45694</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45835</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45629</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45835</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45835</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45835</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45835</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45679</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45077</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45646</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45965</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45965</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45661</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45104</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45841</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45646</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45712</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44852</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45113</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44741</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45841</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45323</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45205</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45692</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45035</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45974</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>44735</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>45278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45659</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45847</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45847</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45161</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45664</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45685</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44746</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45978</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45978</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44810</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45859</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44722</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>44741</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45160</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45469</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45691</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45708</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45708</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45708</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44859</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>44832</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45476</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45691</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45691</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45035</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45670</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>44966</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45369</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45981</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44617</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45040</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45013</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45111</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45264</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45880</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44895</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45342</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>46099</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>46100</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>46100</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>46100</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>46100</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44883</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>46100</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45971</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45496</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45496</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46104</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45247</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>46104</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>46105</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45596</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45688</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45328</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45484</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>46104</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45412</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44897</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45702</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45582</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45988</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45646</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45992</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45989</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>45992</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45992</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45992</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45992</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45992</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45992</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45992</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45708</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45740</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45077</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44960</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>45990</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45992</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45740</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45807</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45993</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44890</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44917</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45996</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45996</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45995</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45996</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45000</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>46000</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>46001</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45562</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45565</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45565</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45560</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45560</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>46006</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44909</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>44987</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46008</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46007</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45344</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45596</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45183</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46010</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45561</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45001</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46010</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45635</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45635</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45635</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>46010</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45443</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>46005</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46010</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46140</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>44610</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45664</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>46012</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>46018</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>46020</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>46020</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45880</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>46021</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45411</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45411</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>44496</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>44867</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46100</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45035</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46030</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>44579</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44657</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46000</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45642</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45496</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46034</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45826</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>46035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>46035</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>45470</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45896</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45232</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>46026</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>46037</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>46037</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45618</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45670</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>46041</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>45589</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>45255</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45909</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>46140</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45831</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45749</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44981</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>44977</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44977</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45342</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44973</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>45981</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>46104</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44974</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45826</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45909</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45187</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45469</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45356</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46045</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46002</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46034</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>46010</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45664</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45664</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45215</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>45841</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41624,7 +41624,7 @@
         <v>46059</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>46065</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>46148</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>46065</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>46148</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45701</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>46149</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>46149</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>46153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>46076</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45687</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>46076</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>46076</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>46079</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>46080</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>46155</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45714</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>46155</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>46009</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>46090</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>46091</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>46159</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45756</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45758</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45685</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>46162</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>46162</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>46149</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>46163</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45378</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45433</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46104</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45679</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46168</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46168</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46027</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46168</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46097</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>46168</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>46182</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46181</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46181</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>46183</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>46183</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>46183</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>46182</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>46182</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45379</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>46200</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>46199</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>46202</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>46202</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>46202</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>46202</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>46206</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>46213</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45960</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45527</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45723</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>46136</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>46138</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46161</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>46265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45501</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>46268</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>46269</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46269</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>46269</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>46231</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>46231</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>46230</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46231</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>46275</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46279</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>46279</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>46237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>46279</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>46279</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>46279</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>46237</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>46282</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>46282</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>46282</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>46238</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46238</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>46238</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>46238</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>46238</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>46238</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>46238</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>46238</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>46281</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>46281</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46240</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>46168</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>46286</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>46283</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45910</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>46241</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>46241</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45890</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>46287</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>46287</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>46076</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>46247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>46289</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>45756</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>46294</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>46291</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>46293</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>46294</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>46293</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46296</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>46296</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         <v>46295</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>45978</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50534,7 +50534,7 @@
         <v>46300</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>46259</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50680,7 +50680,7 @@
         <v>46259</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>46302</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>46262</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>46262</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>44739</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>44944</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44956</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45476</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>44945</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>45028</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>46189</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45412</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>44490</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45035</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45712</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45376</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45915</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45194</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45642</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>46026</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>46087</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46008</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>44868</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44886</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44999</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45239</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45436</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44977</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45463</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>45915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45708</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45260</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45622</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44951</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45618</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45254</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45251</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45572</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45826</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>46037</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45701</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44977</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45835</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>46190</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>46279</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46212</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>46296</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>46296</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44481</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44617</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44854</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44778</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44550</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44635</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44586</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44634</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44558</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44658</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44550</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44789</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44480</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44617</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44565</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44676</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44558</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44552</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44543</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44841</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>44746</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>44620</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44837</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44783</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44800</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44839</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44526</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44529</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44558</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44620</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44620</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45412</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45392</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45204</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45677</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44897</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45463</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45558</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45371</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45462</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45385</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45385</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45635</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45309</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45106</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45393</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45663</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45327</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44664</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44859</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45379</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45264</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45381</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45224</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45098</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45553</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45720</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44490</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45379</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45712</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45212</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45212</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45379</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45659</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45392</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45463</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45562</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45505</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45279</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45463</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45110</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44580</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45886</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45663</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45887</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45676</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45296</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44946</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45075</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44897</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45603</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45889</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45890</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45799</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45341</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45691</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45303</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45463</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45441</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44859</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>44859</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45040</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44546</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44546</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45688</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45632</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45663</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45706</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45161</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44985</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>44854</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44861</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45915</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44503</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45484</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45558</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>44897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44897</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45771</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45399</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45533</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44937</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45390</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45683</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44914</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45016</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45751</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45925</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45792</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45219</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45925</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45643</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45323</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45792</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45009</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45232</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45639</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45659</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45664</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45699</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45688</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44859</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45639</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45932</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45499</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45140</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45700</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45660</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45644</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45530</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45330</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45224</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45208</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45936</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45653</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45688</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45142</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45729</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45091</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45230</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45204</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45629</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45385</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45224</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45938</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45939</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45943</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45575</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>44867</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45943</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45225</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45945</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45225</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45946</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45946</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45813</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45350</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45950</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45665</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45947</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>45949</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45573</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>45098</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45670</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45824</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45826</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45952</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45827</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45827</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45827</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45827</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45618</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45251</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45954</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45953</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45012</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45956</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45958</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45831</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45694</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45835</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45629</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45835</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45835</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45835</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45835</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45679</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45077</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45646</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45965</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45965</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45661</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45104</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45841</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45968</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45646</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45712</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44852</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45113</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>44741</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45841</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45323</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45205</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45692</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45035</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45701</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45974</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>44735</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>45278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45659</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45847</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45847</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45161</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45664</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45685</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44746</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45978</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45978</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44810</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45859</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44722</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>44741</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45160</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45469</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45691</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45708</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45708</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45708</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44859</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>44832</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45476</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45691</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45691</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45035</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45670</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>44966</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45369</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45981</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44617</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45040</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45013</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45111</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45264</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45880</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44895</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45342</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>46099</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>46100</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>46100</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>46100</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>46100</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44883</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>46100</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45971</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45496</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45496</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46104</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45247</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>46104</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>46105</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45596</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45688</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45328</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45484</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>46104</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45412</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44897</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45702</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45582</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45988</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45646</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>45992</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>45989</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>45992</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45992</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45992</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45992</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45992</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45992</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45992</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45708</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45740</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45077</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>44960</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>45990</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45992</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45740</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45807</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45993</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44890</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44917</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45996</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45996</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45995</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45996</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45000</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>45999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>46000</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>46001</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45562</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>45565</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>45565</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45560</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45560</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>46006</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44909</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>44987</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46008</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46007</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45344</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45596</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45183</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46010</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45561</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45001</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46010</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45635</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45635</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45635</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>46010</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45443</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>46005</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46010</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46140</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>44610</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45664</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>46012</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>46018</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>46020</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>46020</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45880</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>46021</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45411</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45411</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>44496</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>44867</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46100</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45035</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46030</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46030</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>44579</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44657</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46000</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45642</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45496</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46034</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45826</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>46035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>46035</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>45470</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45896</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45232</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>46026</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>46037</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>46037</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45618</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45670</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>46041</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>45589</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39726,7 +39726,7 @@
         <v>45255</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45909</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>46140</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45831</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45749</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44981</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>44977</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44977</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45342</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44973</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>45981</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>46104</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44974</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45826</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45909</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45187</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45469</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45356</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46045</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46002</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46034</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>46010</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45664</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45664</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45215</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>45841</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41624,7 +41624,7 @@
         <v>46059</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41697,7 +41697,7 @@
         <v>46065</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>46148</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>46065</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>46148</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45701</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>46149</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>46149</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>46153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>46076</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45687</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>46076</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>46076</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42583,7 +42583,7 @@
         <v>46079</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>46080</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>46155</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45714</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>46155</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>46009</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>46090</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>46091</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43172,7 +43172,7 @@
         <v>46159</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45756</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45758</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45685</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>46162</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>46162</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>46149</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>46163</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45378</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45433</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46104</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45679</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46168</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>46168</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46027</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46168</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46097</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>46168</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>46182</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46181</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46181</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>46183</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>46183</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>46183</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>46182</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>46182</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45379</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>46197</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>46200</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>46199</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>46202</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>46202</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>46202</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>46202</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>46206</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>46213</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45960</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45527</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45723</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>46136</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>46138</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46161</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>46265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45501</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>46268</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>46269</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46269</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>46269</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>46231</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>46231</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>46230</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46231</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>46273</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>46275</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>46279</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>46279</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>46237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>46279</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>46279</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>46279</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>46237</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>46282</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>46282</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>46282</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>46238</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46238</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>46238</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>46238</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>46238</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>46238</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>46238</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>46238</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>46281</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>46281</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46240</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>46168</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>46286</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>46283</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45910</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>46241</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>46241</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>45890</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>46287</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>46287</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>46076</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>46247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>46289</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>45756</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>46294</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>46291</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>46293</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>46294</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>46293</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46296</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50310,7 +50310,7 @@
         <v>46296</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50383,7 +50383,7 @@
         <v>46295</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>45978</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50534,7 +50534,7 @@
         <v>46300</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>46259</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50680,7 +50680,7 @@
         <v>46259</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>46302</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>46262</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>46262</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>44739</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>44944</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44956</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45476</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>44945</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>45028</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>46189</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>46052</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45463</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45376</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44490</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45035</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>46026</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46279</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45194</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46008</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>44868</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45618</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44886</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45621</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45826</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45835</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44977</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45622</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44999</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45701</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>46037</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44951</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>46127</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>46279</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>45239</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45463</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45054</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>46212</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>46296</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46296</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>46260</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45260</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44617</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44778</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44868</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44634</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44558</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44746</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44868</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44634</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44491</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44558</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44658</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44676</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44558</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44746</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44783</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44617</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44837</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44620</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44839</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44558</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44550</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44789</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44491</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44841</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44800</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44529</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44565</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44620</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44620</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44558</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44852</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45469</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44897</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44946</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45369</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45328</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45392</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45659</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45565</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45565</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45751</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45582</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45646</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45142</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45278</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45618</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45205</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45390</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44854</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45558</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44861</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44859</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45688</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44867</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45638</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45701</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45688</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45573</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>45603</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45385</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45661</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45561</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45463</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45040</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45463</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45469</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44832</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45496</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45496</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45484</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45393</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45677</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45635</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45505</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45659</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45110</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45702</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44810</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44937</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44994</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45632</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45224</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45086</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45208</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45399</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45356</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45679</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45469</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45663</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>44746</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>46026</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>46002</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45341</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45884</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45887</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45826</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>46104</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45884</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44741</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45664</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45225</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45886</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45799</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45909</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44735</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45909</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44657</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45670</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45841</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45880</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45643</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45897</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45575</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>46140</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45981</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45589</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45496</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45009</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45187</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>46100</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45296</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46140</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45642</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45915</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45917</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45035</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>44981</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45342</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>44897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44897</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44741</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45771</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45925</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45664</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45664</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45925</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45701</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46148</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46148</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46149</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46149</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44977</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>44977</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45932</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45687</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45932</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45936</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>46153</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44617</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>44664</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45560</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45560</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45938</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45939</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45943</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45945</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>46155</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45945</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45946</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45946</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45371</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45947</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45949</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45953</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45952</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45953</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45714</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45000</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45954</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45956</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45629</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>44565</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45646</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45965</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45965</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45965</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45712</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45224</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44876</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45968</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>46009</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>46159</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45553</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>46162</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46162</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45161</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>46163</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44973</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45685</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45756</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>45974</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45975</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45381</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45708</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45708</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45708</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45758</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45978</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45691</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>44909</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>46104</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45215</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45533</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44859</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45712</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45679</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45433</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>46149</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45988</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45098</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45098</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45706</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>46027</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45378</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46097</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45708</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45989</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45992</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45992</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45992</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45740</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45740</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45992</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>45993</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>46168</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45990</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45992</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45992</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45992</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45385</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45385</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45251</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45995</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45996</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45996</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45996</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45729</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45303</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>46168</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46000</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46168</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45629</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>46001</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45161</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>46006</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>46007</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>46005</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45476</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>46008</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>46010</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45635</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45635</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46010</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45670</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46012</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45443</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46010</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45635</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>44883</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>46018</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46020</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>46020</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>46021</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44895</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45035</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45670</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45596</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45691</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>46030</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46030</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>46034</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45001</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46035</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>46035</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46037</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>46037</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46041</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>44867</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45183</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>46183</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>46183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>46045</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46010</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46181</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>44890</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45412</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46181</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45558</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46183</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46182</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44546</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46182</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>46059</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45484</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45644</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44490</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>46065</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>46065</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45470</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45691</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45691</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44852</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>46076</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46076</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>46076</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>46079</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46080</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45350</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45379</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>46090</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46091</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45379</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>46100</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46100</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>46100</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46100</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46099</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45971</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46100</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46104</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46104</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46104</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46104</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46104</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45344</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>46105</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45264</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45075</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45012</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>46197</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>44897</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45562</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46202</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>46202</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>45807</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46202</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45077</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>46199</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46200</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45688</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45255</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45596</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>46202</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>46133</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45665</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45379</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45826</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45412</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45232</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>46000</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45664</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45749</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>44496</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45054</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45212</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45212</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45562</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45040</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45664</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46213</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45077</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>44579</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45527</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45204</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45960</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46136</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46138</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45723</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45264</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46161</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45501</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45323</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45106</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45342</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45016</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44546</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>46230</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>45463</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>46273</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>46231</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>46231</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46275</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>46231</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>46279</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>44960</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>46279</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>46279</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>46279</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>46237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45232</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>46238</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46237</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>44722</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46238</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>46238</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>44872</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>46281</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>46281</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>46238</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>46238</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42585,7 +42585,7 @@
         <v>46238</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46238</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>46238</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>44985</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>46282</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>46240</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>46283</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>46282</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>44917</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>45890</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44580</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45663</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>45910</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45309</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45098</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>46241</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>46241</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>46286</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45204</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45255</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45530</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45411</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45411</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45104</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>46076</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>46287</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45323</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>46287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44897</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>45618</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45327</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46289</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>45663</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>46291</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>46174</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45720</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45756</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>44859</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46247</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>46293</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>46293</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>44610</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45392</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44897</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44966</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>46294</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46295</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45379</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45013</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45676</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>46294</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45653</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45328</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45441</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>46296</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>46296</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45639</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>44995</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>45692</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46300</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45978</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44914</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45683</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>46259</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>46302</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45219</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46259</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45792</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>46307</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45792</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>46262</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45499</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45140</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45699</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>44859</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45659</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45639</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45700</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45688</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45660</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>46262</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>46265</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45330</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>45230</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46309</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46168</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>46309</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>46265</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>46268</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45813</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>46269</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>46269</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>46311</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46311</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>46269</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46311</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>46311</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45824</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45826</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45827</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>45827</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45827</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45827</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45831</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50345,7 +50345,7 @@
         <v>45694</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>45835</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45835</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45835</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45835</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>45835</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45841</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45841</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45847</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45847</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45685</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>45859</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45881</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45880</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44944</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>44739</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>44956</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>45476</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>44945</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45028</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51830,7 +51830,7 @@
         <v>46189</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>46052</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>45043</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45463</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45995</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45376</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>45712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>44490</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45035</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45664</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>45824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44658</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45915</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>46026</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46279</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45194</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>46008</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>44868</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45618</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44886</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45621</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45254</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45826</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45835</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44977</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45622</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44999</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45251</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45701</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>46037</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46190</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44951</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>46127</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>46279</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>45239</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45463</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45054</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>46212</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>46296</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>46296</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>46260</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45260</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44854</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44868</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44617</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44778</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44550</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44868</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44634</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>44635</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44558</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44746</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44868</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>44634</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44491</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44558</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44658</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44676</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44558</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44746</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44783</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44617</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44837</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44620</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44839</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44558</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44550</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44789</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44491</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44841</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44800</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44529</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44565</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44543</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44620</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44620</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44558</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44852</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45469</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44897</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44946</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45369</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45328</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45392</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45659</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45565</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45565</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45751</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45582</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45646</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45142</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45278</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45618</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45205</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45390</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44854</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45558</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44861</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44859</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45688</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44867</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45638</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45701</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45688</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45573</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>45603</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45385</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45661</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45561</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45463</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45040</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45463</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45469</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44832</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45496</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45496</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45484</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45393</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45677</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45635</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45505</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45659</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45110</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45702</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44810</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44937</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44994</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45632</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45224</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45086</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45208</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45399</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45356</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45679</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45469</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45663</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>44746</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>46026</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>46002</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45341</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45884</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45887</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45826</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>46104</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45884</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44741</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45664</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45225</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45886</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45799</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45909</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44735</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45909</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>44657</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45670</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45841</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45880</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45643</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45897</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45575</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>46140</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45981</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45589</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45496</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45009</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45187</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>46100</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45296</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46140</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45642</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45915</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45917</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45035</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>44981</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45342</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>44897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44897</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44741</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45771</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45925</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45664</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45664</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45925</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45701</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46148</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46148</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46149</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46149</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44977</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>44977</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45932</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45687</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45932</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45936</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>46153</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44617</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>44664</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45560</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45560</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45938</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45939</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45943</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45945</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>46155</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45945</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45946</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45946</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45371</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45947</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45949</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45953</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45952</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45953</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45714</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45000</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45954</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45956</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45629</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>44565</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>45646</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45965</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45965</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45965</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45712</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45224</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44876</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45968</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>46009</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>46159</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45553</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>46162</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46162</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45161</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>46163</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44973</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45685</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45756</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>45974</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45975</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45381</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45708</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45708</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45708</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45758</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45978</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45691</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>44909</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>46104</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45215</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45533</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44859</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45712</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45679</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45433</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>46149</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45988</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45098</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45098</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45706</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>46027</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45378</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46097</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45708</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45989</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45992</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45992</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45992</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45740</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45740</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>45992</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>45993</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>46168</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45990</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45992</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45992</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45992</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45385</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45385</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45251</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45995</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45996</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45996</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45996</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45729</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45303</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>46168</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46000</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46168</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45629</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>46001</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45161</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>46006</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>46007</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>46005</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45476</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>46008</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>46010</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45635</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45635</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>46010</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45670</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>46012</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45443</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46010</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45635</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>44883</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>46018</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46020</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>46020</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>46021</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44895</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45035</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45670</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45596</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45691</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>46030</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>46030</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>46034</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45001</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46035</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>46035</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>46037</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>46037</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>46041</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>44867</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45183</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>46183</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>46183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>46045</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46010</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46181</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>44890</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45412</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46181</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45558</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46183</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>46182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46182</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44546</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46182</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>46059</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45484</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45644</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44490</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>46065</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>46065</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45470</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45691</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45691</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44852</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>46076</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46076</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>46076</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>46079</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46080</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45350</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45379</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45112</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>46090</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46091</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45379</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>46100</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46100</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>46100</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46100</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46099</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45971</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46100</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46104</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46104</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46104</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>46104</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46104</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45344</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>46105</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45264</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45075</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45012</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>46197</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>44897</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45562</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46202</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>46202</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>45807</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46202</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45077</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>46199</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46200</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45688</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45255</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45596</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>46202</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>46133</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45665</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45379</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45826</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45412</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45232</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>46000</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45664</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45749</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>44496</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45054</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45212</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45212</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45562</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45040</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>45664</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46213</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45077</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         <v>44579</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>45527</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45204</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45960</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46136</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46138</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45723</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45264</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46161</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45501</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45323</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45106</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45342</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45016</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>44546</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>46230</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>45463</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>46273</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>46231</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>46231</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46275</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>46231</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>46279</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>44960</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>46279</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>46279</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>46279</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>46279</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>46237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45232</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>46238</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46237</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>44722</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46238</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>46238</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>44872</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>46281</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>46281</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>46238</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>46238</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42585,7 +42585,7 @@
         <v>46238</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46238</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>46238</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>44985</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>46282</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>46240</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>46283</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>46282</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>44917</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>45890</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>44580</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45663</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>45910</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45309</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45098</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>46241</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>46241</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>46286</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45204</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45255</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45530</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45411</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45411</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45104</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>46076</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>46287</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45323</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>46287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44897</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>45618</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45327</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46289</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>45663</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>46291</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>46174</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45720</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45756</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>44859</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46247</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>46293</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>46293</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>44610</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45392</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44897</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44966</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>46294</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46295</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45379</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45013</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45676</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>46294</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45653</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45328</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45441</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>46296</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>46296</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45639</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>44995</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>45692</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46300</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45978</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>44914</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45683</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>46259</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>46302</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45219</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46259</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45792</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>46307</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45792</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>46262</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45499</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45140</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45699</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>44859</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45659</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45639</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45700</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45688</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45660</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>46262</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>46265</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45330</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>45230</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46309</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46168</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>46309</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>46265</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49152,7 +49152,7 @@
         <v>46268</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45813</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>46269</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>46269</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>46311</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46311</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>46269</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46311</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>46311</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45824</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45826</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45827</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>45827</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45827</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45827</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45831</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50345,7 +50345,7 @@
         <v>45694</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>45835</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45835</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45835</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>45835</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>45835</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45841</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45841</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45847</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45847</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45685</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>45859</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45881</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45880</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44944</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>44739</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>44956</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>45476</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>44945</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45028</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51830,7 +51830,7 @@
         <v>46189</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>46052</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45043</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45412</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45664</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45824</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45035</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45376</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44658</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44733</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45915</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>46279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>46026</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45194</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>46008</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45727</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45915</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44886</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>46190</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>45239</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>45708</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46037</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46212</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45054</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>46296</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>46296</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>46260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>46127</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45545</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45826</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>46316</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45835</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44951</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>45618</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44999</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45642</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45463</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45622</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45254</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45572</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>44868</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44587</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44617</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44852</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44854</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44550</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44778</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44868</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44634</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44635</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44558</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44746</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44868</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44634</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44741</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44558</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44658</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44558</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>44692</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44746</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44526</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44617</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44620</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44837</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44839</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44558</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44558</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44841</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>44529</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44800</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44565</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44620</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44620</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44852</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>44558</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>45886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45887</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45344</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45890</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45327</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45183</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45897</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45799</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45561</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45212</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45412</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45884</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45411</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45411</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45392</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45884</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45204</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45756</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45758</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45685</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44579</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45915</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>46162</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45915</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45642</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>46149</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>46163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45433</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45470</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45232</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45618</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>46104</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45670</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46168</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>46168</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46027</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46168</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45255</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45925</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45925</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44981</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45932</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45342</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44974</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45469</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45356</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45215</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45938</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45385</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45385</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45393</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45379</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45946</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45224</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45098</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45371</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45945</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45945</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45328</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45950</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45462</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45949</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46182</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44876</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45635</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45309</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>46181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46183</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>46183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45954</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45953</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46182</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45956</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46182</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45958</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45663</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45264</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45720</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45379</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45712</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45968</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45379</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45659</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>46197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45279</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45975</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45978</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>46200</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45708</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45708</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45708</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44580</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>46202</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>45663</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45981</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46202</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45463</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45676</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45296</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44946</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44897</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45505</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46206</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45988</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45638</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45691</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45989</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45992</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45992</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45708</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45740</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45990</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45992</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45740</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46213</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45996</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45996</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45441</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45995</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45463</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45664</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45996</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45960</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45527</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45688</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46000</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46001</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45723</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46136</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46138</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46161</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45501</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46231</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>46231</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46008</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>46230</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46231</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>46007</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>46010</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>46010</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>46279</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>46279</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>46237</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>46010</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45635</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45635</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45635</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46010</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45443</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46005</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46010</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46279</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>46012</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46018</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>46282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46020</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46020</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45683</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46021</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46238</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>46238</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>44914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46238</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>46238</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46238</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46238</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46238</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>46238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>46030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45792</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>46281</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>46281</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>46030</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45219</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46240</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>46286</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>46034</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>46035</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45659</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>46037</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>46037</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45699</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44859</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45910</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45639</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>46241</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46241</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45890</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45499</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46041</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45700</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46287</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45660</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46287</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>46076</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45330</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46045</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45688</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>46247</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45756</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45230</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46059</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46294</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46065</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45813</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46291</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46293</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46065</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46294</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46293</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46076</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46296</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45824</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>46076</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46076</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45826</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46079</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>46296</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45827</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46080</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46295</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45827</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45831</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45694</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45835</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46300</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>46090</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>46091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45835</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45835</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45835</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45835</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45841</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45603</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>46099</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46100</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46100</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46100</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46100</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46100</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45971</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46104</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45341</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46104</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45847</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46105</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46259</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45847</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46104</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46104</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>46259</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45685</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>46302</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45859</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45807</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>46262</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>44992</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>45881</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44859</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>44859</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45880</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45632</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45663</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>46307</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>44985</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44854</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46262</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>44861</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>46309</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>46168</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45558</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44897</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>44897</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>46309</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44960</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>46140</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>44610</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45664</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45880</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>46268</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>46311</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46311</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>46311</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>46311</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>46100</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>44937</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>46314</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>46269</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44657</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44966</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45390</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>46000</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45751</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>46269</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45496</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46269</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45826</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46314</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46314</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45896</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46026</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45589</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45009</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45232</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45639</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45978</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45909</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46140</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45831</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45749</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46104</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45688</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>46316</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45826</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45909</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45187</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>46002</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>46273</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>46034</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45664</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45664</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>46317</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>46317</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46275</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45530</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45841</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45224</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45208</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>46294</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>46148</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45142</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>46148</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45701</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46149</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45091</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>46149</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45687</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45575</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>44867</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>46155</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45714</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>46155</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45350</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>46009</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>46159</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45573</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45618</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45012</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45629</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45679</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45646</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45661</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45104</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>45646</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45712</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45113</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45323</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45692</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45035</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45701</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45659</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45161</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45664</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44810</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45691</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>44832</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45476</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45691</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45691</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45670</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>45369</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44617</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45040</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45013</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44895</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>44883</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45496</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45496</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45596</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45688</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45412</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>44897</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45702</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45054</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45077</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>44897</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45463</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45086</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45106</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45496</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44664</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45381</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44872</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45379</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45392</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45562</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45110</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45075</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45303</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45463</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45040</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>45112</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>44546</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47145,7 +47145,7 @@
         <v>44546</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45706</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45161</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>44610</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>44503</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>45484</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>45771</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44994</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45399</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45533</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45016</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44995</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>45643</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45323</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45664</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45644</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45653</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>45729</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45204</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45629</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45385</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45224</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45225</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45665</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45098</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45670</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45251</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>44852</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>44741</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45205</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>44735</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45278</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45255</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>44746</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>44722</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>44741</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45160</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>45469</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>44859</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45264</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>45342</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>45247</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>45328</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45484</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45582</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45646</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>44960</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>44890</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50747,7 +50747,7 @@
         <v>44917</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>44565</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45000</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45562</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45565</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45565</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45560</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         <v>45560</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>44909</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>44987</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>44739</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>44944</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>44956</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45476</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44945</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45028</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>46189</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>

--- a/Översikt LULEÅ.xlsx
+++ b/Översikt LULEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45957</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45453</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>45696</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45461</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45664</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45433</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45463</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>46052</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>45043</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>45412</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45664</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>45824</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45035</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>46099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45376</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44658</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44733</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45915</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>46279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>46026</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45194</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>46087</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45239</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>46008</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>44868</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45727</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45915</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44886</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>46190</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>45239</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45436</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>45708</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46037</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46212</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45054</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>46296</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>46296</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45834</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>46260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>46127</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45545</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45826</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>46316</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45835</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44951</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>45618</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44999</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45642</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45463</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>45622</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45254</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>45251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45572</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>44868</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44587</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44617</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44852</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44854</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44550</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44778</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44868</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44634</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44635</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44558</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44746</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44868</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44634</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44741</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44558</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44658</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44558</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>44692</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44746</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44526</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44617</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44620</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44837</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44839</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44558</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44558</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44841</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>44529</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44800</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44565</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44620</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44620</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44852</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>44558</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>45886</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45887</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45344</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45890</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45327</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45183</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45897</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45799</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45561</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45212</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45212</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>45412</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45884</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45411</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45411</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>44496</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45392</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45884</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45204</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45756</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45758</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45685</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44579</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45915</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>46162</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45915</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45642</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>46149</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>46163</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45433</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45470</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45232</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45618</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>46104</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45679</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45670</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>46168</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>46168</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46027</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46168</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45255</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45925</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45925</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44981</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45932</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>44977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45342</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44974</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45469</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45356</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45215</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45938</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45385</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45385</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45393</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45379</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45946</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45224</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45098</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45946</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45371</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45945</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45945</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45328</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45950</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45462</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45949</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46182</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44876</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45947</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45635</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45952</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45309</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>46181</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46183</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>46183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45954</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45953</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46182</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45956</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46182</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45958</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45663</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45264</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45720</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45379</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45712</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45968</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45379</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45659</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>46197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45279</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45975</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45978</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>46200</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45708</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45708</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45708</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44580</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>46202</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>46202</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>45663</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45981</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>46202</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45463</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45676</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45296</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44946</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44897</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45505</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46206</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45988</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45992</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45638</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45691</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45989</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45992</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45992</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45992</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45708</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45740</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45990</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45992</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45740</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>46213</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45996</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45996</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45441</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45995</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45463</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45664</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>45996</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45960</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45527</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45688</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46000</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46001</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45723</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46136</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46138</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46161</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45501</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46231</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>46231</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46008</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>46230</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46231</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>46007</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>46010</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>46010</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>46279</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>46279</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>46237</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>46010</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45635</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45635</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45635</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46010</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45443</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46005</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46010</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46279</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>46012</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46018</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>46282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46020</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46020</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45683</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46021</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46238</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>46238</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>44914</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46238</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>46238</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46238</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46238</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46238</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>46238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>46030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         <v>45792</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>46281</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>46281</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>46030</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45219</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46240</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>46286</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>46034</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>46035</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45659</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>46037</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>46037</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45699</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>44859</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45910</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45639</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>46241</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46241</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45890</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45499</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46041</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45700</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46287</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45660</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46287</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>46076</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45330</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46045</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45688</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>46247</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45756</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45230</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46059</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46294</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>46065</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45813</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46291</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46293</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46065</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46294</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46293</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46076</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46296</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45824</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>46076</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46076</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45826</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46079</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>46296</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45827</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46080</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46295</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45827</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45831</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45694</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45835</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46300</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>46090</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>46091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45835</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45835</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45835</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45835</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45841</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45603</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>46099</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46100</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46100</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46100</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46100</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46100</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45971</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46104</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45341</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46104</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45847</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46105</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46259</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45847</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46104</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46104</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>46259</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45685</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>46302</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45859</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45807</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>46262</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>44992</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>45881</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>44859</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>44859</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45880</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45632</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45663</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>46307</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>44985</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>44854</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46262</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>44861</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>46309</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>46168</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45558</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44897</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>44897</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37127,7 +37127,7 @@
         <v>46309</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44960</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>46140</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>44610</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45664</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45880</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>46268</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>46311</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46311</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>46311</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>46311</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>46100</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>44937</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>46314</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>46269</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44657</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44966</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45390</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>46000</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45751</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>46269</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>45496</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46269</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45826</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46314</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46314</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45896</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46026</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45589</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45009</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45232</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45639</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45978</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45909</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46140</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45831</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45749</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46104</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45688</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>46316</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45826</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45909</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45187</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>46002</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>46273</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>46034</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45664</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45664</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>46317</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>46317</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46275</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45530</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45841</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45224</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45208</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>46294</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>46148</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45142</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>46148</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45701</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46149</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45091</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>46149</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45687</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45575</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>44867</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>46155</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45714</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>46155</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45350</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>46009</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>46159</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45573</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45618</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45012</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45629</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45679</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45646</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45661</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45104</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>45646</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45712</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45113</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45323</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45692</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45035</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45701</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45659</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45161</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45664</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44810</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45691</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>44832</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45476</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45691</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45691</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45670</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>45369</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44617</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45040</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45013</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>45111</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44895</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>44883</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45496</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45496</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45596</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>45688</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45412</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>44897</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45702</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45054</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45077</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>44897</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45463</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45086</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45106</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45496</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44664</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45381</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44872</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45379</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45392</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45562</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45110</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45075</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45303</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45463</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45040</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>45112</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>44546</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47145,7 +47145,7 @@
         <v>44546</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45706</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45161</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>44610</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>44503</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>45484</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>45771</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44994</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45399</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45533</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45016</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>44995</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>45643</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45323</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45664</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45644</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45653</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>45729</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45204</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45629</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45385</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45224</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45225</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45665</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45098</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45670</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>45251</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>44852</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>44741</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45205</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>44735</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45278</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45255</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>44746</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>44722</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>44741</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45160</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>45469</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>44859</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45264</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>45342</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50236,7 +50236,7 @@
         <v>45247</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>45328</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45484</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45582</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45646</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>44960</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>44890</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50747,7 +50747,7 @@
         <v>44917</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>44565</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45000</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45562</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45565</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45565</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45560</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         <v>45560</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>44909</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>44987</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>44739</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>44944</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>44956</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>45476</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44945</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45028</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>46189</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
